--- a/SISAB/dados/visita_domiciliar/pessoas_idosas_sisab.xlsx
+++ b/SISAB/dados/visita_domiciliar/pessoas_idosas_sisab.xlsx
@@ -5,16 +5,18 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/juliasbardelatti/Desktop/macbook/julia/projetos/ImpulsaGov/pessoa_idosa/dados/SISAB/dados/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/juliasbardelatti/Desktop/macbook/julia/projetos/ImpulsaGov/dados-para-midia/SISAB/dados/visita_domiciliar/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD5F926B-8883-3E49-B4D0-137903F933DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{752E5D01-EFCE-194A-B1F3-DD7CF91BA1B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29360" yWindow="720" windowWidth="28800" windowHeight="15780" xr2:uid="{17FF875B-B3C1-F949-B649-9AA6C895FAA4}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="3" xr2:uid="{17FF875B-B3C1-F949-B649-9AA6C895FAA4}"/>
   </bookViews>
   <sheets>
     <sheet name="demência" sheetId="1" r:id="rId1"/>
     <sheet name="visita" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
   <si>
     <t>Ano</t>
   </si>
@@ -57,7 +59,37 @@
     <t>Total visitas domicilares para pessoas idosas</t>
   </si>
   <si>
-    <t>Percentual</t>
+    <t>Total visitas domicilares para adultos</t>
+  </si>
+  <si>
+    <t>total visitas para criancas</t>
+  </si>
+  <si>
+    <t>ano</t>
+  </si>
+  <si>
+    <t>total visita domiciliar idosos (60 ou mais)</t>
+  </si>
+  <si>
+    <t>total visitas criancas (0-14)</t>
+  </si>
+  <si>
+    <t>total adultos 15-59</t>
+  </si>
+  <si>
+    <t>https://educa.ibge.gov.br/jovens/conheca-o-brasil/populacao/18318-piramide-etaria.html?utm_source=chatgpt.com</t>
+  </si>
+  <si>
+    <t>total visita geral</t>
+  </si>
+  <si>
+    <t>total visita geral idoso</t>
+  </si>
+  <si>
+    <t>total visita crianca</t>
+  </si>
+  <si>
+    <t>total adulto</t>
   </si>
 </sst>
 </file>
@@ -67,7 +99,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -88,6 +120,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -111,12 +149,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -593,16 +632,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD69C0F5-6576-A442-ACA2-DB2B853DBD5C}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.83203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="38.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="32.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -615,8 +655,11 @@
       <c r="D1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>2025</v>
       </c>
@@ -626,12 +669,9 @@
       <c r="C2" s="1">
         <v>235293802</v>
       </c>
-      <c r="D2" s="3">
-        <f t="shared" ref="D2:D8" si="0">C2/B2</f>
-        <v>0.59130240360832131</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D2" s="3"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2024</v>
       </c>
@@ -641,12 +681,9 @@
       <c r="C3" s="1">
         <v>359700686</v>
       </c>
-      <c r="D3" s="3">
-        <f t="shared" si="0"/>
-        <v>0.57338345253071066</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D3" s="3"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>2023</v>
       </c>
@@ -656,12 +693,9 @@
       <c r="C4" s="1">
         <v>346014616</v>
       </c>
-      <c r="D4" s="3">
-        <f t="shared" si="0"/>
-        <v>0.56839205178622665</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D4" s="3"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>2022</v>
       </c>
@@ -671,12 +705,9 @@
       <c r="C5" s="1">
         <v>303301597</v>
       </c>
-      <c r="D5" s="3">
-        <f t="shared" si="0"/>
-        <v>0.55429657023300982</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D5" s="3"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>2021</v>
       </c>
@@ -686,12 +717,9 @@
       <c r="C6" s="1">
         <v>225665288</v>
       </c>
-      <c r="D6" s="3">
-        <f t="shared" si="0"/>
-        <v>0.57352507483169191</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D6" s="3"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>2020</v>
       </c>
@@ -701,12 +729,9 @@
       <c r="C7" s="1">
         <v>172124639</v>
       </c>
-      <c r="D7" s="3">
-        <f t="shared" si="0"/>
-        <v>0.57960333322738533</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D7" s="3"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>2019</v>
       </c>
@@ -716,9 +741,11 @@
       <c r="C8" s="1">
         <v>177517261</v>
       </c>
-      <c r="D8" s="3">
-        <f t="shared" si="0"/>
-        <v>0.59415570832942943</v>
+      <c r="D8" s="3"/>
+    </row>
+    <row r="14" spans="1:5" ht="18" x14ac:dyDescent="0.2">
+      <c r="C14" s="5">
+        <v>344295862</v>
       </c>
     </row>
   </sheetData>
@@ -727,4 +754,219 @@
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A78CEA6F-DA60-244E-8F97-68B3B70A0C9A}">
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="35.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>2019</v>
+      </c>
+      <c r="B2" s="5">
+        <v>75108435</v>
+      </c>
+      <c r="C2" s="5">
+        <v>58700796</v>
+      </c>
+      <c r="D2" s="5">
+        <v>202861057</v>
+      </c>
+      <c r="E2" s="3">
+        <f>B2/D2</f>
+        <v>0.37024570467460394</v>
+      </c>
+      <c r="F2" s="1">
+        <f>SUM(B2:D2)</f>
+        <v>336670288</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+      <c r="C3" s="5">
+        <v>53289538</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68E8655B-57AF-0845-8A81-BC7A8BA427D6}">
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="18" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>2025</v>
+      </c>
+      <c r="B2" s="5">
+        <v>444493569</v>
+      </c>
+      <c r="C2" s="5">
+        <v>102329747</v>
+      </c>
+      <c r="D2" s="5">
+        <v>70494117</v>
+      </c>
+      <c r="E2" s="5">
+        <v>267713507</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="18" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>2024</v>
+      </c>
+      <c r="B3" s="5">
+        <v>696494055</v>
+      </c>
+      <c r="C3" s="5">
+        <v>156777260</v>
+      </c>
+      <c r="D3" s="5">
+        <v>113763570</v>
+      </c>
+      <c r="E3" s="5">
+        <v>420565093</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="18" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>2023</v>
+      </c>
+      <c r="B4" s="5">
+        <v>668320813</v>
+      </c>
+      <c r="C4" s="5">
+        <v>147521766</v>
+      </c>
+      <c r="D4" s="5">
+        <v>110982262</v>
+      </c>
+      <c r="E4" s="5">
+        <v>405032444</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="18" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>2022</v>
+      </c>
+      <c r="B5" s="5">
+        <v>595938444</v>
+      </c>
+      <c r="C5" s="5">
+        <v>127646646</v>
+      </c>
+      <c r="D5" s="5">
+        <v>99115744</v>
+      </c>
+      <c r="E5" s="5">
+        <v>360543130</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="18" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>2021</v>
+      </c>
+      <c r="B6" s="5">
+        <v>449534825</v>
+      </c>
+      <c r="C6" s="5">
+        <v>93282145</v>
+      </c>
+      <c r="D6" s="5">
+        <v>67082794</v>
+      </c>
+      <c r="E6" s="5">
+        <v>254547083</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="18" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>2020</v>
+      </c>
+      <c r="B7" s="5">
+        <v>336987279</v>
+      </c>
+      <c r="C7" s="5">
+        <v>70216329</v>
+      </c>
+      <c r="D7" s="5">
+        <v>53289538</v>
+      </c>
+      <c r="E7" s="5">
+        <v>190808751</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="18" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>2019</v>
+      </c>
+      <c r="B8" s="5">
+        <v>344295862</v>
+      </c>
+      <c r="C8" s="5">
+        <v>75108435</v>
+      </c>
+      <c r="D8" s="5">
+        <v>58700796</v>
+      </c>
+      <c r="E8" s="5">
+        <v>202861057</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>